--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.66.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.66.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.66.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.66.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -601,24 +601,28 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: are the following:â€” Attorney Gener</t>
+          <t>L16: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: Collyer, 33 ； 9 Jurist, 224; Brown</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: are the following :â€”Attorney General vs. Berry, 2</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]59</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]59</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: 59</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: !</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]59</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,14 +668,22 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: ï¼�</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
-      <c r="N3" s="1" t="inlineStr"/>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>L42: isolated marker/symbol line :: 59</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L75: isolated marker/symbol line :: !</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
@@ -969,7 +981,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1003,12 +1015,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
